--- a/TestData/LV_TMTT0048687_VerifyTheCaptialSolutionChangesImplementedOnJobTypeobject.xlsx
+++ b/TestData/LV_TMTT0048687_VerifyTheCaptialSolutionChangesImplementedOnJobTypeobject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC280CC1-3F98-4D59-8705-239F227AE4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963EBDFE-BEE6-4DD9-8C32-A0695C0F2A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -283,7 +283,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,18 +423,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,12 +513,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="45"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -856,7 +844,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -872,13 +860,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -894,16 +877,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1357,12 +1340,12 @@
       <c r="L1" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1383,13 +1366,13 @@
       <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K2" s="2" t="s">
@@ -1403,7 +1386,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1424,13 +1407,13 @@
       <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="21" t="s">
+      <c r="J3" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -1444,7 +1427,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1465,13 +1448,13 @@
       <c r="G4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J4" s="21" t="s">
+      <c r="J4" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -1485,7 +1468,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -1506,13 +1489,13 @@
       <c r="G5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="21" t="s">
+      <c r="J5" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -1526,7 +1509,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -1547,13 +1530,13 @@
       <c r="G6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -1567,7 +1550,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1588,13 +1571,13 @@
       <c r="G7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -1608,7 +1591,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1629,13 +1612,13 @@
       <c r="G8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -1649,7 +1632,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1670,13 +1653,13 @@
       <c r="G9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K9" s="2" t="s">
@@ -1690,7 +1673,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1711,13 +1694,13 @@
       <c r="G10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -1731,7 +1714,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1752,13 +1735,13 @@
       <c r="G11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="2" t="s">
@@ -1772,7 +1755,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -1793,13 +1776,13 @@
       <c r="G12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K12" s="2" t="s">
@@ -1813,7 +1796,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1834,13 +1817,13 @@
       <c r="G13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -1854,7 +1837,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1875,13 +1858,13 @@
       <c r="G14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K14" s="2" t="s">
@@ -1895,7 +1878,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1916,13 +1899,13 @@
       <c r="G15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J15" s="21" t="s">
+      <c r="J15" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K15" s="2" t="s">
@@ -1936,7 +1919,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1957,13 +1940,13 @@
       <c r="G16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="J16" s="18" t="s">
         <v>66</v>
       </c>
       <c r="K16" s="2" t="s">
@@ -1977,7 +1960,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1998,13 +1981,13 @@
       <c r="G17" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J17" s="21" t="s">
+      <c r="J17" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K17" s="2" t="s">
@@ -2018,34 +2001,34 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="17" t="s">
+      <c r="C18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="16" t="s">
+      <c r="E18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="21" t="s">
+      <c r="J18" s="18" t="s">
         <v>65</v>
       </c>
       <c r="K18" s="2" t="s">

--- a/TestData/LV_TMTT0048687_VerifyTheCaptialSolutionChangesImplementedOnJobTypeobject.xlsx
+++ b/TestData/LV_TMTT0048687_VerifyTheCaptialSolutionChangesImplementedOnJobTypeobject.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963EBDFE-BEE6-4DD9-8C32-A0695C0F2A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C886F20-5691-47D5-B853-EFE30D3201C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>

--- a/TestData/LV_TMTT0048687_VerifyTheCaptialSolutionChangesImplementedOnJobTypeobject.xlsx
+++ b/TestData/LV_TMTT0048687_VerifyTheCaptialSolutionChangesImplementedOnJobTypeobject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C886F20-5691-47D5-B853-EFE30D3201C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573DD4E4-74B1-482D-9EA7-2B3B432E7150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -48,9 +48,6 @@
     <t>6511</t>
   </si>
   <si>
-    <t>Admin</t>
-  </si>
-  <si>
     <t>App Name</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>Profile</t>
   </si>
   <si>
-    <t>CF Financial User</t>
-  </si>
-  <si>
     <t>Debt Financing</t>
   </si>
   <si>
@@ -219,9 +213,6 @@
     <t>5261</t>
   </si>
   <si>
-    <t>Denis Collins</t>
-  </si>
-  <si>
     <t>Primary Line of Business</t>
   </si>
   <si>
@@ -277,6 +268,15 @@
   </si>
   <si>
     <t>IsActive</t>
+  </si>
+  <si>
+    <t>Ajay Nair</t>
+  </si>
+  <si>
+    <t>System Admin</t>
+  </si>
+  <si>
+    <t>User</t>
   </si>
 </sst>
 </file>
@@ -1218,18 +1218,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1247,12 +1247,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1270,12 +1270,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1289,551 +1289,551 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" customWidth="1"/>
-    <col min="13" max="13" width="8.42578125" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="I1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="M1" s="19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I2" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J2" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="L2" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I3" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="L5" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I7" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J7" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="M7" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I8" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="M8" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I9" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="M9" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I10" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="M10" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I11" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="M11" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I12" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="M12" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="H13" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I13" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="L13" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1844,201 +1844,201 @@
         <v>1</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="L14" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="H15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I15" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="G16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I16" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="I17" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="G18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="13" t="s">
+      <c r="H18" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>23</v>
-      </c>
       <c r="I18" s="17" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2057,74 +2057,74 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
